--- a/doc/docs/词条配置.xlsx
+++ b/doc/docs/词条配置.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\proj\unityProj\Line\doc\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6C12E13-551B-43CD-B853-2D213B9A136F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{511FDA76-6BC6-4CD7-88D9-BFE5035A6144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="504" windowWidth="31008" windowHeight="16560" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Attr" sheetId="3" r:id="rId1"/>
-    <sheet name="AttrType" sheetId="4" r:id="rId2"/>
+    <sheet name="StockAttr" sheetId="3" r:id="rId1"/>
+    <sheet name="PlayerAttr" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="127">
   <si>
     <t>Horizontal</t>
   </si>
@@ -41,14 +41,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>Attr</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>enum#AttrType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>name#string</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -65,26 +57,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>格式化描述</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>icon#string</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>图标</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>originValue#float</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>初始值</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>社交</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -113,34 +85,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>标识</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>social</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>wisdom</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>charisma</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>courage</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>calmness</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>fanaticism</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>AttrType</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -189,22 +133,389 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>每回合摸牌数+1，每回合失去1</t>
-  </si>
-  <si>
-    <t>每回合能量恢复+1</t>
-  </si>
-  <si>
-    <t>玩家影响力+10%</t>
-  </si>
-  <si>
-    <t>玩家交易数量+10%</t>
-  </si>
-  <si>
-    <t>环境对市场价格影响-2%</t>
-  </si>
-  <si>
-    <t>环境对市场价格影响+2%</t>
+    <t>未知</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>unknown</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>描述</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>符号</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>公司发展有一些变化，但还不清楚有什么影响</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>effect1#string[]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合开始时效果</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>effect2#string[]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>股价计算前效果</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>effect3#string[]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>回合清算时效果</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>[]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>爬升</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>高歌</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Add#0.3","UpScale1.2"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Add#0.1","UpScale#1.1"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>火箭</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Add#0.5","UpScale#1.3"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>滑坡</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>fall_slow</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Add#-0.1","DownScale#1.1"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>摔落</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>fall_middle</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Add#-0.3","DownScale#1.1"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>断崖</t>
+  </si>
+  <si>
+    <t>fall_fast</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Add#-0.5","DownScale#1.3"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>摇摆</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>pingpong</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["UpScaleLast#0.85","DownScaleLast#1.15"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>懒散</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Scale#0.3"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>lazy</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>敏感</t>
+  </si>
+  <si>
+    <t>sensitive</t>
+  </si>
+  <si>
+    <t>盲从</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Transfer#1#2#0.08"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Transfer#1#3#0.08"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>blindly</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>腐败</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>混乱</t>
+  </si>
+  <si>
+    <t>["Add#0.4%1","Scale#1.3%1","Add#-0.6%1"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>corruption</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>创新</t>
+  </si>
+  <si>
+    <t>chaotic</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>innovative</t>
+  </si>
+  <si>
+    <t>每日5%的公司实力变为市场敏感度，5%的公司实力变为行业冲击乘数，交易日结束后各增加5%并给予【滑坡*】</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>每回合8%行业冲击乘数变为公司实力</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Transfer#3#1#0.08"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>衰老</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>aging</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>每日公司业绩额外上升0.1，若业绩上升，再放大10%</t>
+  </si>
+  <si>
+    <t>每日公司业绩额外上升0.3，若业绩上升，再放大20%</t>
+  </si>
+  <si>
+    <t>每日公司业绩额外上升0.5，若业绩上升，再放大30%</t>
+  </si>
+  <si>
+    <t>每日公司业绩额外下降0.1，若业绩下降，再放大10%</t>
+  </si>
+  <si>
+    <t>每日公司业绩额外下降0.3，若业绩下降，再放大20%</t>
+  </si>
+  <si>
+    <t>每日公司业绩额外下降0.5，若业绩下降，再放大30%</t>
+  </si>
+  <si>
+    <t>每日，若上个交易日公司业绩上升，则此次业绩缩减15%，若上个交易日公司业绩下降，则此次业绩放大15%</t>
+  </si>
+  <si>
+    <t>每日，公司业绩变化缩减30%</t>
+  </si>
+  <si>
+    <t>每日，1/3概率业绩上升0.4，1/3概率业绩放大30%，1/3概率业绩下降0.6</t>
+  </si>
+  <si>
+    <t>每日8%的公司实力变为市场敏感度</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>每日8%的公司实力变为行业冲击乘数</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>每日公司业绩额外下降0.15，交易日结束时该值增加0.2</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>生长</t>
+  </si>
+  <si>
+    <t>up_slow</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>up_middle</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>up_fast</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>growing</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Transfer#3#1#0.08%0.33"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Transfer#1#2#0.05*1","Transfer#1#3#0.05*1"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Add#-0.15*1"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["GrowAdd#1#0.2"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Add#0.2*1"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["GrowAdd#1#0.1"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>扩张</t>
+  </si>
+  <si>
+    <t>expanding</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>每日业绩额外上升0.2，交易日结束时该值增加0.1，3/1概率8%行业冲击乘数变为公司实力</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Transfer#1#2#0.2*1"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["GrowAdd#1#-0.08","GrowAdd#2#-0.07"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>精简</t>
+  </si>
+  <si>
+    <t>streamline</t>
+  </si>
+  <si>
+    <t>["Transfer#3#1#0.1*1"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Scale#1.35*2"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Scale#0.8*2"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["GrowAdd#1#0.08","GrowAdd#2#0.05"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>每日业绩缩减20%，交易日结束时该值减少5%，10%行业冲击乘数变为公司实力，交易日结束时该值增加8%</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>每日业绩扩大35%，交易日结束时该值减少7%，20%公司实力变为市场敏感度，交易日结束时该值减少8%</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>整顿</t>
+  </si>
+  <si>
+    <t>每日5%市场敏感度和5%行业冲击乘数变为公司实力，交易日结束后各增加3%，1/3概率移除一条负面属性*</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>rectify</t>
+  </si>
+  <si>
+    <t>["Transfer#2#1#0.05*1","Transfer#3#1#0.05*1"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["GrowAdd#1#0.03","AttrPurify#1%0.3"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>冒险</t>
+  </si>
+  <si>
+    <t>adventure</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>每日8%行业冲击乘数变为市场敏感度</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Transfer#3#2#0.08"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>停滞</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>stagnant</t>
+  </si>
+  <si>
+    <t>每回合8%市场敏感度变为行业冲击乘数</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["Transfer#2#3#0.08"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>["GrowAdd#1#0.05","AttrAdd#5#-1"]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>StockAttr</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -317,7 +628,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -325,9 +636,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1">
@@ -345,13 +653,13 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -622,15 +930,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.6640625" customWidth="1"/>
+    <col min="1" max="1" width="22.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.59765625" customWidth="1"/>
     <col min="3" max="3" width="21.06640625" customWidth="1"/>
-    <col min="4" max="4" width="28.86328125" customWidth="1"/>
-    <col min="5" max="5" width="24.3984375" customWidth="1"/>
-    <col min="6" max="6" width="18.19921875" customWidth="1"/>
+    <col min="4" max="4" width="41.796875" customWidth="1"/>
+    <col min="5" max="5" width="52.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="48.73046875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20.46484375" customWidth="1"/>
     <col min="8" max="8" width="21.33203125" customWidth="1"/>
     <col min="9" max="9" width="23.19921875" bestFit="1" customWidth="1"/>
@@ -641,7 +949,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>126</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -655,21 +963,23 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>19</v>
+        <v>2</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>12</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="1"/>
+        <v>32</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -677,14 +987,12 @@
       <c r="L2" s="1"/>
     </row>
     <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
+      <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="7"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="6"/>
     </row>
     <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
@@ -714,9 +1022,11 @@
       <c r="F5" s="1">
         <v>1</v>
       </c>
-      <c r="G5" s="1"/>
+      <c r="G5" s="1">
+        <v>1</v>
+      </c>
       <c r="H5" s="1"/>
-      <c r="I5" s="4"/>
+      <c r="I5" s="3"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
@@ -730,24 +1040,26 @@
     </row>
     <row r="7" spans="1:12" ht="16.149999999999999" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>20</v>
+        <v>3</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>28</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="1"/>
+        <v>33</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>35</v>
+      </c>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
@@ -757,109 +1069,489 @@
       <c r="A8">
         <v>1</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="I8" s="5"/>
-      <c r="J8" s="5"/>
+      <c r="B8" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
     </row>
     <row r="9" spans="1:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>2</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="B9" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="I9" s="5"/>
-      <c r="J9" s="5"/>
+      <c r="G9" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
     </row>
     <row r="10" spans="1:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>3</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>23</v>
+      <c r="B10" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>90</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10" s="1"/>
-      <c r="F10" s="9">
-        <v>0</v>
-      </c>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5"/>
+        <v>77</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
     </row>
     <row r="11" spans="1:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>4</v>
       </c>
-      <c r="B11" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="B11" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="F11" s="9">
-        <v>0</v>
+      <c r="G11" s="10" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>5</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="B12" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="F12" s="9">
-        <v>0</v>
+      <c r="C12" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15.75" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>6</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A14" s="1">
+        <v>7</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A15" s="1">
+        <v>8</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A16" s="1">
+        <v>9</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>10</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" t="s">
+        <v>59</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>11</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A19" s="1">
+        <v>12</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A20" s="1">
+        <v>13</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E20" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A21" s="1">
+        <v>14</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A22" s="1">
+        <v>15</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="E22" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A23" s="1">
+        <v>16</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E23" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A24" s="1">
+        <v>17</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E24" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A25" s="1">
         <v>18</v>
       </c>
-      <c r="C13" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" t="s">
-        <v>44</v>
-      </c>
-      <c r="F13" s="9">
-        <v>0</v>
+      <c r="B25" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C25" t="s">
+        <v>105</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E25" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A26" s="1">
+        <v>19</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C26" t="s">
+        <v>114</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="E26" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A27" s="1">
+        <v>20</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="A28" s="1">
+        <v>21</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="C28" t="s">
+        <v>122</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -877,91 +1569,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>29</v>
+      <c r="A1" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>32</v>
+      <c r="A2" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
-        <v>33</v>
+      <c r="A3" s="6" t="s">
+        <v>19</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>13</v>
+      <c r="C3" s="7" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
-        <v>34</v>
+      <c r="A4" s="6" t="s">
+        <v>20</v>
       </c>
       <c r="B4" s="1">
         <v>2</v>
       </c>
-      <c r="C4" s="8" t="s">
-        <v>14</v>
+      <c r="C4" s="7" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
-        <v>35</v>
+      <c r="A5" s="6" t="s">
+        <v>21</v>
       </c>
       <c r="B5" s="1">
         <v>3</v>
       </c>
-      <c r="C5" s="8" t="s">
-        <v>15</v>
+      <c r="C5" s="7" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
-        <v>36</v>
+      <c r="A6" s="6" t="s">
+        <v>22</v>
       </c>
       <c r="B6">
         <v>4</v>
       </c>
-      <c r="C6" s="8" t="s">
-        <v>16</v>
+      <c r="C6" s="7" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
-        <v>37</v>
+      <c r="A7" s="6" t="s">
+        <v>23</v>
       </c>
       <c r="B7" s="1">
         <v>5</v>
       </c>
-      <c r="C7" s="8" t="s">
-        <v>17</v>
+      <c r="C7" s="7" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15.75" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
-        <v>38</v>
+      <c r="A8" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="B8" s="1">
         <v>6</v>
       </c>
-      <c r="C8" s="8" t="s">
-        <v>18</v>
+      <c r="C8" s="7" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
